--- a/docs/specs/whereisit-api-spec-v2.xlsx
+++ b/docs/specs/whereisit-api-spec-v2.xlsx
@@ -150,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2797" uniqueCount="1265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2797" uniqueCount="1267">
   <si>
     <t>어디갔지 | API 명세서</t>
   </si>
@@ -287,7 +287,7 @@
     <t>미정</t>
   </si>
   <si>
-    <t>지원 언어 범위, 토큰 설정, 실제 코드표·상세 API 매핑, 이메일 제공자·검증·보존기간.</t>
+    <t>지원 언어 범위, 토큰 설정, 이메일 제공자·검증·보존기간, 공통코드 실제 계약·코드표, 일반 정상 빈 결과·오류 봉투 세부 구조.</t>
   </si>
   <si>
     <t>구성</t>
@@ -311,7 +311,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>YAML 파싱·$ref·샘플94건·DB72컬럼 대조는 수행. 실제 HTTP·JWT·경찰청 키·SMTP·배치는 미실행.</t>
+    <t>YAML 파싱·$ref·샘플94건·DB72컬럼 대조 수행. 2026-09-26 일반·포털 목록·상세 HTTP 실호출 완료. 공통코드·JWT·SMTP·배치·제품 기능 테스트는 미실행.</t>
   </si>
   <si>
     <t>D01·S07</t>
@@ -419,7 +419,7 @@
     <t>오류</t>
   </si>
   <si>
-    <t>공식 목록 문서 확인 · 실제 인증키 호출·상세 응답은 미검증</t>
+    <t>2026-09-26 일반·포털 목록·상세 실제 호출 완료 · 공통코드는 승인대기</t>
   </si>
   <si>
     <t>09_내부배치</t>
@@ -593,7 +593,7 @@
     <t>외부 상세</t>
   </si>
   <si>
-    <t>공식 목록 계약만 재확인. 상세API 경로·연락처 매핑은 아직 미확정; NULL 예약컬럼에 추측값을 넣지 않음.</t>
+    <t>일반·포털 목록·상세 API 실호출을 확인했습니다. 상세 응답은 fdPlace→found_place, tel→storage_phone, uniq→description으로 매핑하며, 상세 호출 실패·미실행 또는 필드 누락 시 관련 DB 컬럼은 NULL을 유지할 수 있습니다. 공통코드 실제 계약과 코드표는 승인대기로 미확정입니다.</t>
   </si>
   <si>
     <t>경찰청 2번 API를 사용한 검색의 생성과 수정, 삭제</t>
@@ -1442,7 +1442,7 @@
     <t>CURRENT=최근 완전성공, ALL=누적 캐시</t>
   </si>
   <si>
-    <t>경찰 상세 API 필드가 미검증인 단계에서는 foundPlace/storagePhone/description을 임의 보완하지 않는다.</t>
+    <t>일반·포털 상세 Client를 사용하며 fdPlace→found_place, tel→storage_phone, uniq→description으로 저장한다. 상세 실패·미실행 시 관련 DB 컬럼은 NULL을 유지할 수 있다.</t>
   </si>
   <si>
     <t>categories</t>
@@ -1454,7 +1454,7 @@
     <t>array&lt;CodeOption&gt;</t>
   </si>
   <si>
-    <t>상세 Client 확정 전에는 신규 상세 호출을 약속하지 않는다.</t>
+    <t>일반·포털 상세 Client는 사용 가능하다. 상세조회 성공 시 매핑 필드와 detail_fetched_at을 저장하고, 실패 시 상세 관련 DB 컬럼은 NULL 유지 가능하다.</t>
   </si>
   <si>
     <t>메일 링크용. 지정하면 scope 대신 해당 알림의 후보를 조회</t>
@@ -2102,7 +2102,7 @@
     <t>먼저 발송 상태 해결; 옛 메일에 새 조건 후보를 혼합하지 않음</t>
   </si>
   <si>
-    <t>상세 매핑 확인 전 null; 보관장소를 복사하지 않음</t>
+    <t>일반·포털 상세 fdPlace → DB found_place; 실패·미실행 시 null</t>
   </si>
   <si>
     <t>습득물.습득_장소</t>
@@ -2135,7 +2135,7 @@
     <t>최대길이 40</t>
   </si>
   <si>
-    <t>상세 매핑 확인 전 null</t>
+    <t>일반·포털 상세 tel → DB storage_phone; 실패·미실행 시 null</t>
   </si>
   <si>
     <t>LostItem.languageCode</t>
@@ -2243,7 +2243,7 @@
     <t>지역_코드</t>
   </si>
   <si>
-    <t>공식 목록 계약 확인 / 실제 키 호출 미검증</t>
+    <t>HTTP 200 · application/xml · 정상 XML Namespace 없음 · 경찰민원24 HTTPS 이미지 접근 확인</t>
   </si>
   <si>
     <t>전체 동기 검색 예산 초과, 제공 가능한 결과 없음</t>
@@ -2495,7 +2495,7 @@
     <t>ChatMessage.role</t>
   </si>
   <si>
-    <t>fdYmd: POLICE 예시 yyyy-MM-dd / PORTAL 예시 yyyyMMdd</t>
+    <t>fdYmd: 실제 일반·포털 yyyy-MM-dd; 공식 문서 호환을 위해 yyyyMMdd도 방어적으로 처리</t>
   </si>
   <si>
     <t>내부 DATE로 정규화</t>
@@ -2546,7 +2546,7 @@
     <t>00=정상 문서 기준</t>
   </si>
   <si>
-    <t>resultMsg/resultMag 표기 차이 실제 응답 확인</t>
+    <t>실제 resultMsg(resultMag는 문서 오타). 정상 response/header/body; 목록·상세 body/items/item</t>
   </si>
   <si>
     <t>reason</t>
@@ -2564,19 +2564,19 @@
     <t>상세 API</t>
   </si>
   <si>
-    <t>아직 호출 경로·상세 필드 매핑 미확정</t>
+    <t>목록 depPlace 제공. 상세 fdPlace·tel·uniq 제공</t>
   </si>
   <si>
     <t>선택언어 설명; 생성 실패면 null</t>
   </si>
   <si>
-    <t>foundPlace/storagePhone/description 예약</t>
+    <t>fdPlace→found_place / tel→storage_phone / uniq→description</t>
   </si>
   <si>
     <t>외부_관리_번호</t>
   </si>
   <si>
-    <t>null 허용</t>
+    <t>상세 성공 시 저장; 실패·미실행 또는 누락 시 null 허용</t>
   </si>
   <si>
     <t>FoundItem.atcId</t>
@@ -2585,7 +2585,7 @@
     <t>분실물_후보.추천_이유</t>
   </si>
   <si>
-    <t>임의 상세 엔드포인트·기관 연락처 생성 금지</t>
+    <t>포털 빈 결과=&lt;items/&gt;. 일반 페이지 범위 초과는 별도 XML 오류 봉투 가능(내부 element 계약 미확정).</t>
   </si>
   <si>
     <t>첨부 SQL v0.3 예약 컬럼</t>
@@ -3584,7 +3584,7 @@
     <t>공식 목록 계약: FD_COL_CD, XML, 일반 습득물</t>
   </si>
   <si>
-    <t>웹 문서 확인 / 키 호출 미검증</t>
+    <t>2026-09-26 실제 목록·상세 호출 검증 완료(요청 URL·Key·실제 응답 원문 미기록); 공통코드는 승인대기</t>
   </si>
   <si>
     <t>비밀번호는 400 VALIDATION_ERROR(fields에 password); ja·KO는 400 UNSUPPORTED_LANGUAGE; 빈 값은 400 VALIDATION_ERROR; 회원 저장 안 함. 경계값 8자·20자는 201</t>
@@ -3851,10 +3851,10 @@
     <t>필터·외부 상세</t>
   </si>
   <si>
-    <t>코드 이름·허용값·출처별 변환은 실제 코드표 확인 후 설정 파일로 제공. 상세 API는 확인 전 미사용.</t>
-  </si>
-  <si>
-    <t>습득장소·연락처·상세설명은 NULL 가능; 가짜 코드/URL을 동작 예제로 넣지 않음</t>
+    <t>일반·포털 상세 API 계약과 fdPlace·tel·uniq 매핑은 확인됨. 공통코드 실제 계약·코드표는 승인대기로 미확정.</t>
+  </si>
+  <si>
+    <t>일반 정상 빈 검색 결과와 페이지 범위 초과 오류 봉투의 세부 구조는 미확정. 상세 실패·미실행·필드 누락 시 관련 DB 컬럼은 NULL 가능.</t>
   </si>
   <si>
     <t>D13</t>
@@ -3911,16 +3911,16 @@
     <t>서버(JVM)·DB 시간대를 Asia/Seoul로 고정하는 방법은 구현 단계에서 정한다.</t>
   </si>
   <si>
-    <t>API v2 · 현재 구현 기준 · 2026-09-25</t>
-  </si>
-  <si>
-    <t>확정 · 이 문서는 현재 구현 기준 API v2 확정본입니다.</t>
+    <t>API v2.1 · 현재 구현 기준 · 2026-09-26</t>
+  </si>
+  <si>
+    <t>확정 · 이 문서는 현재 구현 기준 API v2.1 확정본입니다.</t>
   </si>
   <si>
     <t>19개 내부 REST 계약 · 배치·외부 API는 별도 구역</t>
   </si>
   <si>
-    <t>API v2 확정본 / 테이블 명세 v2 기준. 원본 Snapshot은 별도 보존.</t>
+    <t>API v2.1 확정본 / 테이블 명세 v2.1 기준. 원본 Snapshot은 별도 보존.</t>
   </si>
   <si>
     <t>필드 누락·빈 문자열·허용 길이 초과·형식 불일치·알 수 없는 JSON 요청 필드는 400 VALIDATION_ERROR</t>
@@ -3945,6 +3945,12 @@
   </si>
   <si>
     <t>Content type is not supported.</t>
+  </si>
+  <si>
+    <t>2026-09-26 일반·포털 목록·상세 실호출 완료 · 공통코드 승인대기 · 일반 정상 빈 결과/오류 봉투 세부 미확정</t>
+  </si>
+  <si>
+    <t>일반·포털 상세 uniq(특이사항/상세텍스트) → DB description; 실패·미실행 시 null</t>
   </si>
 </sst>
 </file>
@@ -20775,7 +20781,7 @@
         <v>254</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>661</v>
+        <v>1266</v>
       </c>
       <c r="G74" s="10" t="s">
         <v>673</v>
@@ -26437,7 +26443,7 @@
     <row r="2" ht="24.0" customHeight="1"/>
     <row r="3" ht="31.5" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>89</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="4">

--- a/docs/specs/whereisit-api-spec-v2.xlsx
+++ b/docs/specs/whereisit-api-spec-v2.xlsx
@@ -155,7 +155,7 @@
     <x:t xml:space="preserve">어디갔지 | API 명세서</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">API v2.2 · Issue #57 구현 기준 · 2026-09-28</x:t>
+    <x:t xml:space="preserve">API v2.3 · Issue #80 구현 기준 · 2026-09-28</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">내부 REST API</x:t>
@@ -173,7 +173,7 @@
     <x:t xml:space="preserve">상태</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">확정 · 이 문서는 Issue #57 구현을 반영한 API v2.2 확정본입니다.</x:t>
+    <x:t xml:space="preserve">확정 · 이 문서는 Issue #80 구현을 반영한 API v2.3 확정본입니다.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">유지</x:t>
@@ -209,7 +209,7 @@
     <x:t xml:space="preserve">검증</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">YAML 파싱·$ref·샘플94건·DB72컬럼 대조와 일반·포털 목록·상세 HTTP 실호출 이력 확인. Issue #57은 Mock/Fake·SQLite 집중 검증을 수행했으며 실제 OpenAI·경찰·포털·SMTP 호출과 MySQL 검증은 수행하지 않음.</x:t>
+    <x:t xml:space="preserve">YAML 파싱·$ref·샘플94건·DB72컬럼 대조와 일반·포털 목록·상세 HTTP 실호출 이력 확인. Issue #57·#80은 Mock/Fake·SQLite 집중 검증을 수행했으며 실제 OpenAI·경찰·포털·SMTP 호출과 MySQL 검증은 수행하지 않음.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">주의</x:t>
@@ -3176,10 +3176,10 @@
     <x:t xml:space="preserve">TC-11</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">AI가 후보 추가·누락·중복·key변경·순위오류·부적절한 추천이유 출력</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AI 응답 전체 폐기; 같은 최대100 후보를 규칙 기반으로 반환; UNAVAILABLE 경고; 임의 사실·후보 미표시</x:t>
+    <x:t xml:space="preserve">AI가 후보 추가·누락·중복·key변경·score오류·부적절한 추천이유 출력</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AI 응답 전체 폐기; 같은 최대20 후보를 규칙 기반으로 반환; UNAVAILABLE 경고; 임의 사실·후보 미표시</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">TC-12</x:t>
@@ -7444,7 +7444,7 @@
         <v>포털기관 목록 2번 API ItemList</v>
       </c>
       <c r="D11" s="10" t="str">
-        <v>productNameKeyword/PRDT_NM·storagePlaceKeyword/DEP_PLACE로 포털만 조회; 일반 경찰청 호출0회; OpenAI rank/reason 반환</v>
+        <v>productNameKeyword/PRDT_NM·storagePlaceKeyword/DEP_PLACE로 포털만 조회; 일반 경찰청 호출0회; OpenAI score·서버 rank 반환</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>63</v>
@@ -7481,10 +7481,10 @@
         <v>79</v>
       </c>
       <c r="C13" s="10" t="str">
-        <v>후보1·100·101건 및 자연키 중복</v>
+        <v>후보1·20·21·72·100·101건 및 자연키 중복</v>
       </c>
       <c r="D13" s="10" t="str">
-        <v>1건 rank=1; 최대100개; 중복 제거·안정 사전축약·RESULT_LIMIT_REACHED; fdSn 문자열 보존</v>
+        <v>1건 rank=1; 최대20개; 중복 제거·결정적 사전축약·RESULT_LIMIT_REACHED; fdSn 문자열 보존</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>63</v>
@@ -7524,7 +7524,7 @@
         <v>AI timeout·429·4xx·5xx·refusal·Schema 오류 / 검색 중 동시 수정</v>
       </c>
       <c r="D15" s="10" t="str">
-        <v>timeout·408·504는504, 429는429; 기타 실패는 UNAVAILABLE+동일 집합 fallback; stale snapshot은409 ITEM_BUSY</v>
+        <v>조건 구조화 timeout·408·504는504, 429는429; 후보 평가 실패는 timeout·429 포함 201+UNAVAILABLE+동일 20건 fallback; stale snapshot은409 ITEM_BUSY</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -9330,7 +9330,7 @@
         <v>1102</v>
       </c>
       <c r="D18" s="8" t="str">
-        <v>설명2,000·장소255·후보 문자열100~300 code point, 최종 OpenAI 요청128KiB, 후보 최대100건. 포털기관 목록 2번 결과를 자연키로 중복 제거하고 안정 축약한다.</v>
+        <v>설명2,000·장소255·후보 문자열100~300 code point, 최종 OpenAI 요청128KiB, 후보 최대20건. 포털기관 목록 2번 결과를 자연키로 중복 제거하고 결정적 축약한다.</v>
       </c>
       <c r="E18" s="8" t="str">
         <v>후보0건은 AI 미호출. API-05 성공·fallback 모두 LostItemCandidate를 저장하지 않고 persisted=false. OpenAI·외부조회는 트랜잭션 밖이며 FoundItem 원본 캐시만 마지막 짧은 트랜잭션에서 upsert. 모델은 OPENAI_MODEL=gpt-4o-mini, 자동 retry/model fallback 없음.</v>
@@ -14766,7 +14766,7 @@
         <v>5</v>
       </c>
       <c r="D29" s="15" t="str">
-        <v>atcId를 openId로 노출하고 fdSn 문자열을 보존한다. 자연키 중복 제거 후 최대 100건을 OpenAI로 랭킹한다.</v>
+        <v>atcId를 openId로 노출하고 fdSn 문자열을 보존한다. 결정적 사전 축약한 최대 20건만 OpenAI로 평가하고 rank는 서버가 부여한다.</v>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
@@ -21149,7 +21149,7 @@
         <v>624</v>
       </c>
       <c r="F101" s="8" t="str">
-        <v>Frontend 호환용 이름. transient 결과 최대100개이며 Candidate Entity 저장을 뜻하지 않음</v>
+        <v>Frontend 호환용 이름. API-05 transient 최대20개이며 Candidate Entity 저장을 뜻하지 않음</v>
       </c>
       <c r="G101" s="8" t="s">
         <v>338</v>
@@ -26313,7 +26313,7 @@
         <v>정수</v>
       </c>
       <c r="F9" s="10" t="str">
-        <v>응답 자연키 중복 제거 후 최대100건 사전 축약</v>
+        <v>응답 자연키 중복 제거 후 최대20건 결정적 사전 축약</v>
       </c>
       <c r="G9" s="10" t="str">
         <v>https://www.data.go.kr/data/15057670/openapi.do</v>

--- a/docs/specs/whereisit-api-spec-v2.xlsx
+++ b/docs/specs/whereisit-api-spec-v2.xlsx
@@ -3696,6 +3696,48 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">동일 API 계약을 YAML로 제공하는 표현 형식</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">TrackedLostItemConditions</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">itemTypeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">API-16 전용 표시 필드(items[].conditions). 사용자가 등록한 물품 종류 표시값으로 API-05 물품명 검색어(productNameKeyword)를 그대로 쓴다. 공식 분류 코드가 아니며 값이 없으면 null. API-16 conditions에는 SearchConditions 8개 필드도 함께 있고, 다른 API의 SearchConditions에는 이 필드가 없다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">분실물_검색_추적.물품명_검색어</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">API-16 전용 표시 필드(items[].conditions). 사용자가 명시한 색상의 짧은 한국어 색상명(예: 검정, 복수는 검정/흰색). 없거나 모호하면 null이며 공식 colorCode가 아니다. 후보(currentCandidate) 값으로 대신하지 않는다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">분실물_검색_추적.표시_색상명</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">물품명_검색어</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">TrackedLostItemConditions.itemTypeName(API-16 전용 표시값)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">API-05 AI 물품명 검색어를 저장하고 추적 매칭에 사용. API-16은 같은 값을 물품 종류로 표시하며 공식 분류 코드가 아님</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">보관장소_검색어</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">API-05 AI 보관장소 검색어를 저장하고 추적 매칭에만 사용</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">표시_색상명</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">TrackedLostItemConditions.colorName(API-16 전용 표시값)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">API-05에서만 AI가 사용자가 명시한 색상을 저장하고 없거나 모호하면 NULL. 공식 색상_코드와 별개이며 기존 행 backfill 없음</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4444,7 +4486,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A5:G130" displayName="SpecTable05" name="SpecTable05" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A5:G132" displayName="SpecTable05" name="SpecTable05" id="6">
   <tableColumns count="7">
     <tableColumn name="자료형" id="1"/>
     <tableColumn name="필드" id="2"/>
@@ -4472,7 +4514,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A5:D82" displayName="SpecTable07" name="SpecTable07" id="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A5:D85" displayName="SpecTable07" name="SpecTable07" id="8">
   <tableColumns count="4">
     <tableColumn name="테이블" id="1"/>
     <tableColumn name="컬럼" id="2"/>
@@ -14738,7 +14780,7 @@
         <v>3</v>
       </c>
       <c r="D27" s="22" t="str">
-        <v>OpenAI로 lostDateFrom/lostDateTo/lostPlaceText/productNameKeyword/storagePlaceKeyword와 ASSISTANT 메시지를 구조화한다.</v>
+        <v>OpenAI로 lostDateFrom/lostDateTo/lostPlaceText/productNameKeyword/storagePlaceKeyword와 ASSISTANT 메시지를 구조화한다. 같은 1회 호출에서 API-16 표시용 colorName(사용자가 명시한 색상의 짧은 한국어 색상명, 없거나 모호하면 null)을 추가로 받아 저장한다(API-05 전용, API-11은 기존 6개 필드).</v>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
@@ -21816,8 +21858,52 @@
         <v>338</v>
       </c>
     </row>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="131" ht="45" customHeight="1">
+      <c r="A131" s="8" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B131" s="8" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>1184</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="132" ht="45" customHeight="1">
+      <c r="A132" s="10" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B132" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="C132" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="D132" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>550</v>
+      </c>
+      <c r="F132" s="10" t="s">
+        <v>1186</v>
+      </c>
+      <c r="G132" s="10" t="s">
+        <v>1187</v>
+      </c>
+    </row>
     <row r="133" ht="15.75" customHeight="1"/>
     <row r="134" ht="15.75" customHeight="1"/>
     <row r="135" ht="15.75" customHeight="1"/>
@@ -25234,9 +25320,48 @@
         <v>890</v>
       </c>
     </row>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="83" ht="45" customHeight="1">
+      <c r="A83" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B83" s="45" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C83" s="45" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D83" s="45" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="84" ht="45" customHeight="1">
+      <c r="A84" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="B84" s="44" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C84" s="44" t="s">
+        <v>761</v>
+      </c>
+      <c r="D84" s="44" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="85" ht="45" customHeight="1">
+      <c r="A85" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B85" s="45" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C85" s="45" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D85" s="45" t="s">
+        <v>1195</v>
+      </c>
+    </row>
     <row r="86" ht="15.75" customHeight="1"/>
     <row r="87" ht="15.75" customHeight="1"/>
     <row r="88" ht="15.75" customHeight="1"/>
